--- a/spec.xlsx
+++ b/spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5145E26A-C761-4B4C-B659-BFD0135EF18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4BB51618-3068-FD40-B64E-9B830EB5B786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>crew_name</t>
   </si>
@@ -64,12 +64,6 @@
     <t>task_agent</t>
   </si>
   <si>
-    <t>agent_role</t>
-  </si>
-  <si>
-    <t>agent_goal</t>
-  </si>
-  <si>
     <t>datadog_log_monitor_reporter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,14 +116,6 @@
   </si>
   <si>
     <t>당신은 클라우드 로깅 인프라 및 Datadog API 전문가입니다. Datadog 로그 파이프라인을 쿼리하고, 적절한 인증을 통해 API 요청을 구성하며, 후속 처리를 위해 구조화된 로그 데이터를 추출하는 데 깊은 경험을 가지고 있습니다. Datadog에 인증하기 위해 DD_API_KEY, DD_APP_KEY 및 DD_SITE 환경 변수를 사용합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent_backstory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent_tool</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -220,7 +206,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DatadogLogsSearchCustomTool</t>
+    <t>custom_tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DatadogLogsSearch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crewai_tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WebsiteSearchTool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persona_role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persona_goal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persona_backstory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -736,10 +746,10 @@
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="38.28515625" customWidth="1"/>
-    <col min="10" max="10" width="34.7109375" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -756,140 +766,149 @@
         <v>4</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="255" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="255" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="164" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
-    <row r="3" spans="1:10" ht="164" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="8" t="s">
+    <row r="4" spans="1:11" ht="203" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="139" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:10" ht="203" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" ht="139" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/spec.xlsx
+++ b/spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4BB51618-3068-FD40-B64E-9B830EB5B786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E999D8A9-403D-F341-AAB3-8DC0763F790B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -202,10 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>생성된 로그 분석 보고서를 Microsoft Outlook을 통해 {recipient_email}로 전송합니다.\n- \"애플리케이션 로그 모니터링 보고서 — {time_range}\"와 같이 명확한 제목을 사용합니다.\n- 전체 마크다운 보고서를 이메일 본문에 포함합니다(가능한 경우 HTML로 서식 지정).\n- 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>custom_tool</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,6 +227,13 @@
   </si>
   <si>
     <t>persona_backstory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성된 로그 분석 보고서를 Microsoft Outlook을 통해 {recipient_email}로 전송합니다.
+    - 제목 : 애플리케이션 로그 모니터링 보고서 ({time_range})
+    - 전체 마크다운 보고서를 이메일 본문에 포함합니다(가능한 경우 HTML로 서식 지정). 
+    - 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +742,7 @@
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" customWidth="1"/>
+    <col min="3" max="3" width="102" customWidth="1"/>
     <col min="4" max="4" width="45.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
@@ -769,19 +772,19 @@
         <v>10</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="J1" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="255" customHeight="1">
@@ -811,10 +814,10 @@
         <v>18</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="164" customHeight="1">
@@ -887,7 +890,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>32</v>

--- a/spec.xlsx
+++ b/spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E999D8A9-403D-F341-AAB3-8DC0763F790B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F799DF59-6113-814C-B391-DCB1E46AE72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -38,6 +38,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>jck</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{8CB70C4E-4FB7-0A4F-8462-4E279CA8A17F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Malgun Gothic"/>
+            <family val="2"/>
+            <charset val="129"/>
+          </rPr>
+          <t>jck:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Malgun Gothic"/>
+            <family val="2"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{FDA50F79-D1D7-184E-8BF0-4FCB108457F5}" keepAlive="1" name="쿼리 - spec" description="통합 문서의 'spec' 쿼리에 대한 연결입니다." type="5" refreshedVersion="0" background="1">
@@ -47,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>crew_name</t>
   </si>
@@ -152,17 +188,6 @@
   </si>
   <si>
     <t>당신은 모니터링 및 인시던트 보고서를 적절한 이해관계자에게 안정적으로 전달하는 역할을 담당합니다. 엔지니어링 팀이 지체 없이 문제에 대응할 수 있도록, 적절한 담당자가 시기적절하고 형식에 맞는 이메일 알림을 확실하게 받을 수 있도록 보장합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다.
-    최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.
-    Datadog 로그 검색 엔드포인트에 대한 API 요청을 구성합니다:
-    - APM 트레이스 엔드포인트: ~/api/v2/spans/events/search
-    - 로그 검색 엔드포인트: ~/api/v2/logs/events/search
-    - 인증 헤더(DD-API-KEY 및 DD-APPLICATION-KEY)에 DD_API_KEY 및 DD_APP_KEY를 사용합니다.
-    - 쿼리 및 시간 범위를 본문(body) 매개변수로 포함하여 POST 요청을 제출합니다.
-    - 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스를 포함한 전체 원본(raw) 로그 데이터를 반환합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -214,10 +239,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WebsiteSearchTool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>persona_role</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -234,6 +255,14 @@
     - 제목 : 애플리케이션 로그 모니터링 보고서 ({time_range})
     - 전체 마크다운 보고서를 이메일 본문에 포함합니다(가능한 경우 HTML로 서식 지정). 
     - 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다:
+    - APM 트레이스 엔드포인트: ~/api/v2/spans/events/search
+    - 로그 검색 엔드포인트: ~/api/v2/logs/events/search
+    - 인증 헤더(DD-API-KEY 및 DD-APPLICATION-KEY)에 DD_API_KEY 및 DD_APP_KEY를 사용합니다.
+    - 쿼리 및 시간 범위를 본문(body) 매개변수로 포함하여 POST 요청을 제출합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -241,7 +270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -270,6 +299,21 @@
       <color rgb="FF0432FF"/>
       <name val="Menlo"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -343,10 +387,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -361,9 +408,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -386,9 +430,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -397,6 +438,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,12 +783,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="102" customWidth="1"/>
     <col min="4" max="4" width="45.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" customWidth="1"/>
@@ -752,86 +799,84 @@
     <col min="10" max="11" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" ht="19">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="199" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="255" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" ht="164" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="18" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>9</v>
@@ -852,48 +897,48 @@
       <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11" ht="203" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
+      <c r="C4" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" ht="139" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="18" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
@@ -916,6 +961,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
